--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/95.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/95.xlsx
@@ -426,13 +426,13 @@
         <v>-8.712699931092288</v>
       </c>
       <c r="E2">
-        <v>-20.9395843756432</v>
+        <v>-10.87581620570312</v>
       </c>
       <c r="F2">
-        <v>-0.227559388754035</v>
+        <v>1.53333787932844</v>
       </c>
       <c r="G2">
-        <v>-20.34097948652121</v>
+        <v>-21.27834059269261</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.04196031216936</v>
       </c>
       <c r="E3">
-        <v>-20.86769937924544</v>
+        <v>-11.3341792878115</v>
       </c>
       <c r="F3">
-        <v>0.05264886627649734</v>
+        <v>1.585519405536254</v>
       </c>
       <c r="G3">
-        <v>-20.67668866747654</v>
+        <v>-20.67907557081036</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.237085207096522</v>
       </c>
       <c r="E4">
-        <v>-21.04421929606443</v>
+        <v>-11.92702446252567</v>
       </c>
       <c r="F4">
-        <v>-0.1273139717185488</v>
+        <v>2.220805612749718</v>
       </c>
       <c r="G4">
-        <v>-19.01816825266692</v>
+        <v>-19.77188512141111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.392083171126293</v>
       </c>
       <c r="E5">
-        <v>-20.76471735183701</v>
+        <v>-13.51943970495291</v>
       </c>
       <c r="F5">
-        <v>0.2708494917468712</v>
+        <v>2.227289304767528</v>
       </c>
       <c r="G5">
-        <v>-19.60342470109975</v>
+        <v>-20.20334024518047</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.50855873172742</v>
       </c>
       <c r="E6">
-        <v>-21.54716520477832</v>
+        <v>-15.010811106847</v>
       </c>
       <c r="F6">
-        <v>0.3564464209175002</v>
+        <v>2.004531565525477</v>
       </c>
       <c r="G6">
-        <v>-18.74788703847698</v>
+        <v>-18.20469769221167</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.614320600469854</v>
       </c>
       <c r="E7">
-        <v>-22.44317360040998</v>
+        <v>-14.97664829893314</v>
       </c>
       <c r="F7">
-        <v>0.03307584486758121</v>
+        <v>2.371023286240981</v>
       </c>
       <c r="G7">
-        <v>-18.10181752376051</v>
+        <v>-18.48089650655307</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.721629383755069</v>
       </c>
       <c r="E8">
-        <v>-22.78837464554069</v>
+        <v>-16.56059982344005</v>
       </c>
       <c r="F8">
-        <v>0.3534698456494318</v>
+        <v>2.687761301917039</v>
       </c>
       <c r="G8">
-        <v>-17.76366681546996</v>
+        <v>-17.01617542761238</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.843717344833513</v>
       </c>
       <c r="E9">
-        <v>-24.35951058860589</v>
+        <v>-16.13418059698177</v>
       </c>
       <c r="F9">
-        <v>0.5886414637096548</v>
+        <v>3.05757088652539</v>
       </c>
       <c r="G9">
-        <v>-16.99755857477229</v>
+        <v>-16.36248669233728</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.971323069653927</v>
       </c>
       <c r="E10">
-        <v>-25.55514546695506</v>
+        <v>-16.0375520186061</v>
       </c>
       <c r="F10">
-        <v>0.1573175739338059</v>
+        <v>2.906486925898382</v>
       </c>
       <c r="G10">
-        <v>-16.58780407701285</v>
+        <v>-16.23433878505763</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.10174339278997</v>
       </c>
       <c r="E11">
-        <v>-25.59568436627173</v>
+        <v>-17.60091257180013</v>
       </c>
       <c r="F11">
-        <v>0.6126504453877168</v>
+        <v>3.010615589838525</v>
       </c>
       <c r="G11">
-        <v>-15.8174368194789</v>
+        <v>-15.64168326734453</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.2261722069734295</v>
       </c>
       <c r="E12">
-        <v>-25.28142185556143</v>
+        <v>-18.30669335979159</v>
       </c>
       <c r="F12">
-        <v>0.5942509500621413</v>
+        <v>3.032518242649053</v>
       </c>
       <c r="G12">
-        <v>-15.38632102662731</v>
+        <v>-13.67129456528064</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.6704787944463744</v>
       </c>
       <c r="E13">
-        <v>-26.10022882631033</v>
+        <v>-17.5587388933667</v>
       </c>
       <c r="F13">
-        <v>1.108618043219973</v>
+        <v>2.91415839735277</v>
       </c>
       <c r="G13">
-        <v>-15.15175894353333</v>
+        <v>-13.9227569833526</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.587375873619805</v>
       </c>
       <c r="E14">
-        <v>-26.15561659189814</v>
+        <v>-19.16940841451886</v>
       </c>
       <c r="F14">
-        <v>0.8579934146898497</v>
+        <v>3.197225241560671</v>
       </c>
       <c r="G14">
-        <v>-14.58790351673912</v>
+        <v>-12.96682206143312</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.514594725588132</v>
       </c>
       <c r="E15">
-        <v>-27.26449496520837</v>
+        <v>-20.88689558056395</v>
       </c>
       <c r="F15">
-        <v>1.135374754661323</v>
+        <v>2.916746172818598</v>
       </c>
       <c r="G15">
-        <v>-14.10009794207305</v>
+        <v>-12.75684077896823</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.436788317669127</v>
       </c>
       <c r="E16">
-        <v>-28.1618981308344</v>
+        <v>-21.29920861048833</v>
       </c>
       <c r="F16">
-        <v>1.388176978825175</v>
+        <v>2.936791138590316</v>
       </c>
       <c r="G16">
-        <v>-14.21070657908564</v>
+        <v>-11.73869905109307</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.317927232486863</v>
       </c>
       <c r="E17">
-        <v>-29.11158705735298</v>
+        <v>-22.34448456636083</v>
       </c>
       <c r="F17">
-        <v>1.561603862507203</v>
+        <v>3.417119640507607</v>
       </c>
       <c r="G17">
-        <v>-13.57982584730335</v>
+        <v>-11.42820629551037</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.113757953420643</v>
       </c>
       <c r="E18">
-        <v>-29.05508981563329</v>
+        <v>-22.83612287547756</v>
       </c>
       <c r="F18">
-        <v>1.640035314263426</v>
+        <v>3.487030754438766</v>
       </c>
       <c r="G18">
-        <v>-13.43515831778274</v>
+        <v>-11.10311734464502</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.784856281706453</v>
       </c>
       <c r="E19">
-        <v>-30.21934689758332</v>
+        <v>-23.08507573404924</v>
       </c>
       <c r="F19">
-        <v>1.528100563866081</v>
+        <v>3.810974632030074</v>
       </c>
       <c r="G19">
-        <v>-12.63011640627047</v>
+        <v>-10.33736498759282</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.295634458884773</v>
       </c>
       <c r="E20">
-        <v>-30.96190568722807</v>
+        <v>-24.10668588475765</v>
       </c>
       <c r="F20">
-        <v>1.774032671768758</v>
+        <v>3.86069032812755</v>
       </c>
       <c r="G20">
-        <v>-12.68890838450239</v>
+        <v>-10.55668200847845</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.621754712463985</v>
       </c>
       <c r="E21">
-        <v>-30.86216831144613</v>
+        <v>-24.609903501912</v>
       </c>
       <c r="F21">
-        <v>2.124220140084813</v>
+        <v>3.668608972467561</v>
       </c>
       <c r="G21">
-        <v>-13.35894624892318</v>
+        <v>-10.73520648722919</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.755163450030041</v>
       </c>
       <c r="E22">
-        <v>-31.62014429085</v>
+        <v>-24.91044020790506</v>
       </c>
       <c r="F22">
-        <v>2.111480809701018</v>
+        <v>3.929442169328607</v>
       </c>
       <c r="G22">
-        <v>-12.6968338305234</v>
+        <v>-9.618920326296799</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.701443278525236</v>
       </c>
       <c r="E23">
-        <v>-31.02947731213352</v>
+        <v>-24.21596701951075</v>
       </c>
       <c r="F23">
-        <v>2.2415854180662</v>
+        <v>3.573623042777249</v>
       </c>
       <c r="G23">
-        <v>-12.8682737418201</v>
+        <v>-10.33532238099508</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.481871466908665</v>
       </c>
       <c r="E24">
-        <v>-31.99791638528087</v>
+        <v>-26.48835980503375</v>
       </c>
       <c r="F24">
-        <v>2.204304980816755</v>
+        <v>3.875965171681963</v>
       </c>
       <c r="G24">
-        <v>-12.75241789012776</v>
+        <v>-10.45430669822203</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.133086404712158</v>
       </c>
       <c r="E25">
-        <v>-31.41064802630715</v>
+        <v>-26.55655862358926</v>
       </c>
       <c r="F25">
-        <v>2.329873855440118</v>
+        <v>3.511134758471754</v>
       </c>
       <c r="G25">
-        <v>-12.17285061420417</v>
+        <v>-9.253012348932234</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.698664845550628</v>
       </c>
       <c r="E26">
-        <v>-32.30281627598031</v>
+        <v>-26.5104134734511</v>
       </c>
       <c r="F26">
-        <v>2.110970856396246</v>
+        <v>3.381546438235006</v>
       </c>
       <c r="G26">
-        <v>-11.84710617532205</v>
+        <v>-9.587470143673723</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.222091678345167</v>
       </c>
       <c r="E27">
-        <v>-32.69556403395455</v>
+        <v>-25.39878178794421</v>
       </c>
       <c r="F27">
-        <v>2.068372334682756</v>
+        <v>3.241161994772707</v>
       </c>
       <c r="G27">
-        <v>-12.1031371462382</v>
+        <v>-9.378832942697775</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.739325298803487</v>
       </c>
       <c r="E28">
-        <v>-33.13860276002097</v>
+        <v>-25.04881225968343</v>
       </c>
       <c r="F28">
-        <v>2.023977890461158</v>
+        <v>3.439936091631343</v>
       </c>
       <c r="G28">
-        <v>-11.14922993346152</v>
+        <v>-10.00821068680524</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.273982546774298</v>
       </c>
       <c r="E29">
-        <v>-33.07469467058772</v>
+        <v>-26.02047787056124</v>
       </c>
       <c r="F29">
-        <v>2.042228517430682</v>
+        <v>3.344356272222742</v>
       </c>
       <c r="G29">
-        <v>-11.78353376933142</v>
+        <v>-8.984911128979896</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.839270221839441</v>
       </c>
       <c r="E30">
-        <v>-31.68888426204943</v>
+        <v>-25.14069499729906</v>
       </c>
       <c r="F30">
-        <v>1.944981055693123</v>
+        <v>3.30000458806086</v>
       </c>
       <c r="G30">
-        <v>-11.98389460645919</v>
+        <v>-8.693444078611382</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.434493169438295</v>
       </c>
       <c r="E31">
-        <v>-31.57553202916343</v>
+        <v>-25.0501481595157</v>
       </c>
       <c r="F31">
-        <v>1.830615316715578</v>
+        <v>3.088315369461816</v>
       </c>
       <c r="G31">
-        <v>-11.60948845869532</v>
+        <v>-9.157489867942102</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.045652053012159</v>
       </c>
       <c r="E32">
-        <v>-31.18835202998162</v>
+        <v>-25.63522700130671</v>
       </c>
       <c r="F32">
-        <v>1.922522522106276</v>
+        <v>3.132882437628197</v>
       </c>
       <c r="G32">
-        <v>-11.77603538368497</v>
+        <v>-8.467254365186218</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.659631482546707</v>
       </c>
       <c r="E33">
-        <v>-31.21835996299345</v>
+        <v>-24.27047626114108</v>
       </c>
       <c r="F33">
-        <v>1.770105081098468</v>
+        <v>3.100969179726177</v>
       </c>
       <c r="G33">
-        <v>-11.60089759302091</v>
+        <v>-9.466761032220818</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.262297888485348</v>
       </c>
       <c r="E34">
-        <v>-30.94563488011851</v>
+        <v>-24.01800024979144</v>
       </c>
       <c r="F34">
-        <v>2.141148372614945</v>
+        <v>3.111388380943853</v>
       </c>
       <c r="G34">
-        <v>-11.99356139943387</v>
+        <v>-8.980124080130111</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.839136060844854</v>
       </c>
       <c r="E35">
-        <v>-30.65214221544439</v>
+        <v>-23.34412256118402</v>
       </c>
       <c r="F35">
-        <v>1.884146160363347</v>
+        <v>3.053993294862412</v>
       </c>
       <c r="G35">
-        <v>-12.12587066245638</v>
+        <v>-8.637939472099962</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.387640239839135</v>
       </c>
       <c r="E36">
-        <v>-29.45285738704503</v>
+        <v>-22.61034674687714</v>
       </c>
       <c r="F36">
-        <v>1.689687662124284</v>
+        <v>3.528081995472872</v>
       </c>
       <c r="G36">
-        <v>-11.13946713466621</v>
+        <v>-8.541741639819818</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9138855713789593</v>
       </c>
       <c r="E37">
-        <v>-30.2229357132344</v>
+        <v>-22.88796031744337</v>
       </c>
       <c r="F37">
-        <v>1.611606209375372</v>
+        <v>3.31292604462493</v>
       </c>
       <c r="G37">
-        <v>-12.02782554576532</v>
+        <v>-9.073143788692551</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.4299369639637671</v>
       </c>
       <c r="E38">
-        <v>-29.83951661171596</v>
+        <v>-21.44954941906898</v>
       </c>
       <c r="F38">
-        <v>1.724592540500569</v>
+        <v>3.454889442884923</v>
       </c>
       <c r="G38">
-        <v>-11.6818073260007</v>
+        <v>-8.907616511728992</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.04461927121684678</v>
       </c>
       <c r="E39">
-        <v>-28.79260134825268</v>
+        <v>-21.77323115571523</v>
       </c>
       <c r="F39">
-        <v>1.655208800639251</v>
+        <v>3.676351710688144</v>
       </c>
       <c r="G39">
-        <v>-12.38829429680887</v>
+        <v>-9.613421510156069</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4909313228499701</v>
       </c>
       <c r="E40">
-        <v>-28.54086347816629</v>
+        <v>-21.50141856035284</v>
       </c>
       <c r="F40">
-        <v>1.817147481610681</v>
+        <v>3.91718270183719</v>
       </c>
       <c r="G40">
-        <v>-12.02758718648649</v>
+        <v>-10.40762138502723</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.8978230746444422</v>
       </c>
       <c r="E41">
-        <v>-27.9345415648053</v>
+        <v>-20.69222553992222</v>
       </c>
       <c r="F41">
-        <v>1.529711192782083</v>
+        <v>3.854062518871435</v>
       </c>
       <c r="G41">
-        <v>-12.7501369242512</v>
+        <v>-10.75208695893393</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.258742336272974</v>
       </c>
       <c r="E42">
-        <v>-28.30676854281378</v>
+        <v>-20.42862306793573</v>
       </c>
       <c r="F42">
-        <v>1.86595571421861</v>
+        <v>3.907663045579483</v>
       </c>
       <c r="G42">
-        <v>-11.89499652709314</v>
+        <v>-10.06867117998895</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.570964769318377</v>
       </c>
       <c r="E43">
-        <v>-27.24124577965299</v>
+        <v>-21.574132267494</v>
       </c>
       <c r="F43">
-        <v>1.839680449375554</v>
+        <v>4.216973480512131</v>
       </c>
       <c r="G43">
-        <v>-12.75621508586131</v>
+        <v>-10.40840929486557</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.839450089581112</v>
       </c>
       <c r="E44">
-        <v>-27.29561463858908</v>
+        <v>-19.20690417930237</v>
       </c>
       <c r="F44">
-        <v>1.940917266314105</v>
+        <v>3.97754723651008</v>
       </c>
       <c r="G44">
-        <v>-13.47313689620926</v>
+        <v>-11.18565586603012</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.072641175677994</v>
       </c>
       <c r="E45">
-        <v>-25.30098939174857</v>
+        <v>-19.32411920051691</v>
       </c>
       <c r="F45">
-        <v>2.182744408483962</v>
+        <v>3.765667973201182</v>
       </c>
       <c r="G45">
-        <v>-12.86171886165234</v>
+        <v>-10.51192674333305</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.277252654671433</v>
       </c>
       <c r="E46">
-        <v>-25.47499600549331</v>
+        <v>-18.09615554622698</v>
       </c>
       <c r="F46">
-        <v>1.680563932345437</v>
+        <v>3.817469409989291</v>
       </c>
       <c r="G46">
-        <v>-13.66284108724611</v>
+        <v>-10.65362140295939</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.460656851423988</v>
       </c>
       <c r="E47">
-        <v>-25.79879548246376</v>
+        <v>-19.29640946806398</v>
       </c>
       <c r="F47">
-        <v>2.23106644337585</v>
+        <v>3.827771416969225</v>
       </c>
       <c r="G47">
-        <v>-13.19809677280661</v>
+        <v>-11.13435565235358</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.630676451624908</v>
       </c>
       <c r="E48">
-        <v>-26.56900739863635</v>
+        <v>-17.8687491669838</v>
       </c>
       <c r="F48">
-        <v>1.668073243790366</v>
+        <v>3.721633030222389</v>
       </c>
       <c r="G48">
-        <v>-13.81880254287395</v>
+        <v>-12.60947184428757</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.793042621135414</v>
       </c>
       <c r="E49">
-        <v>-24.55315266564788</v>
+        <v>-17.04303174489919</v>
       </c>
       <c r="F49">
-        <v>2.076617107678534</v>
+        <v>4.156933605551906</v>
       </c>
       <c r="G49">
-        <v>-12.95856887140372</v>
+        <v>-12.33225669246562</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.954278665409444</v>
       </c>
       <c r="E50">
-        <v>-25.08933757357807</v>
+        <v>-17.64587579022229</v>
       </c>
       <c r="F50">
-        <v>1.53634850427369</v>
+        <v>3.694714780777665</v>
       </c>
       <c r="G50">
-        <v>-13.36204823009347</v>
+        <v>-11.74289682283687</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.122144026276502</v>
       </c>
       <c r="E51">
-        <v>-25.09603518663542</v>
+        <v>-17.85345198178589</v>
       </c>
       <c r="F51">
-        <v>1.66913432675371</v>
+        <v>3.640297061817249</v>
       </c>
       <c r="G51">
-        <v>-13.19307467522353</v>
+        <v>-11.69596652927216</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.299641523783961</v>
       </c>
       <c r="E52">
-        <v>-22.62582959950937</v>
+        <v>-16.44646416455072</v>
       </c>
       <c r="F52">
-        <v>1.703974273187463</v>
+        <v>3.97807144316809</v>
       </c>
       <c r="G52">
-        <v>-13.14249616047455</v>
+        <v>-11.54305574135876</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.485817730751002</v>
       </c>
       <c r="E53">
-        <v>-23.56801937307126</v>
+        <v>-16.52026923392773</v>
       </c>
       <c r="F53">
-        <v>1.841953067364209</v>
+        <v>3.876150465274069</v>
       </c>
       <c r="G53">
-        <v>-13.30476586062746</v>
+        <v>-12.26526118238739</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.681369727240352</v>
       </c>
       <c r="E54">
-        <v>-23.61812693796613</v>
+        <v>-16.44748759967646</v>
       </c>
       <c r="F54">
-        <v>1.912344044187746</v>
+        <v>3.791363601679187</v>
       </c>
       <c r="G54">
-        <v>-14.38581788538539</v>
+        <v>-12.18383500430348</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.884987645277207</v>
       </c>
       <c r="E55">
-        <v>-23.81148824961965</v>
+        <v>-14.70400246435333</v>
       </c>
       <c r="F55">
-        <v>1.935011626955431</v>
+        <v>3.837983152711979</v>
       </c>
       <c r="G55">
-        <v>-14.19724590092297</v>
+        <v>-12.4817178919271</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.092667384841294</v>
       </c>
       <c r="E56">
-        <v>-22.06382333278744</v>
+        <v>-15.2999813430808</v>
       </c>
       <c r="F56">
-        <v>1.733237991092953</v>
+        <v>3.760210522616578</v>
       </c>
       <c r="G56">
-        <v>-14.19765475329707</v>
+        <v>-11.05392594847699</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.300681229531004</v>
       </c>
       <c r="E57">
-        <v>-21.9522145623944</v>
+        <v>-14.97894423525503</v>
       </c>
       <c r="F57">
-        <v>1.777946009085809</v>
+        <v>3.512659867268323</v>
       </c>
       <c r="G57">
-        <v>-13.80260238827753</v>
+        <v>-11.62522017109793</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.502485061982052</v>
       </c>
       <c r="E58">
-        <v>-22.29632424528925</v>
+        <v>-15.27803182956562</v>
       </c>
       <c r="F58">
-        <v>1.960970150615399</v>
+        <v>3.775502786936062</v>
       </c>
       <c r="G58">
-        <v>-13.40099348781746</v>
+        <v>-12.82318742212076</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.689493183839902</v>
       </c>
       <c r="E59">
-        <v>-21.89216699705269</v>
+        <v>-13.88732840486204</v>
       </c>
       <c r="F59">
-        <v>1.736863093933394</v>
+        <v>3.928781763961868</v>
       </c>
       <c r="G59">
-        <v>-14.28287978238729</v>
+        <v>-12.85498521202546</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.854803313214556</v>
       </c>
       <c r="E60">
-        <v>-21.06884513771814</v>
+        <v>-13.54373043953005</v>
       </c>
       <c r="F60">
-        <v>1.444751705242419</v>
+        <v>3.40630134539924</v>
       </c>
       <c r="G60">
-        <v>-13.89652256522665</v>
+        <v>-13.11292305717224</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.991786774286637</v>
       </c>
       <c r="E61">
-        <v>-20.90117838758415</v>
+        <v>-12.6842758860883</v>
       </c>
       <c r="F61">
-        <v>1.655344999347979</v>
+        <v>3.238046845237038</v>
       </c>
       <c r="G61">
-        <v>-14.8622550466696</v>
+        <v>-12.85723307244663</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.094260227855464</v>
       </c>
       <c r="E62">
-        <v>-20.79797899342335</v>
+        <v>-13.59805854220008</v>
       </c>
       <c r="F62">
-        <v>1.728250901165234</v>
+        <v>3.880526244718428</v>
       </c>
       <c r="G62">
-        <v>-14.19055032256979</v>
+        <v>-13.43543971415358</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.15881410677722</v>
       </c>
       <c r="E63">
-        <v>-20.07293407700326</v>
+        <v>-13.87958924278293</v>
       </c>
       <c r="F63">
-        <v>1.205664374306272</v>
+        <v>3.409465589818288</v>
       </c>
       <c r="G63">
-        <v>-13.97856119423533</v>
+        <v>-13.53568634362825</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.183871251123196</v>
       </c>
       <c r="E64">
-        <v>-19.90792554111177</v>
+        <v>-14.01338753581356</v>
       </c>
       <c r="F64">
-        <v>1.472957507596395</v>
+        <v>3.753768006952571</v>
       </c>
       <c r="G64">
-        <v>-14.4122674889714</v>
+        <v>-14.15791661991642</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.169605977047333</v>
       </c>
       <c r="E65">
-        <v>-19.91702324539317</v>
+        <v>-13.14277935089092</v>
       </c>
       <c r="F65">
-        <v>2.02272676278796</v>
+        <v>3.692545103673512</v>
       </c>
       <c r="G65">
-        <v>-15.42496171416169</v>
+        <v>-14.15278527433055</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.117475172102886</v>
       </c>
       <c r="E66">
-        <v>-20.85900470915071</v>
+        <v>-12.93923350119415</v>
       </c>
       <c r="F66">
-        <v>1.86538241267722</v>
+        <v>3.835278183008408</v>
       </c>
       <c r="G66">
-        <v>-13.79541188336623</v>
+        <v>-13.21664575946314</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.030075680397657</v>
       </c>
       <c r="E67">
-        <v>-20.55050694585217</v>
+        <v>-13.26425113767267</v>
       </c>
       <c r="F67">
-        <v>1.400297080196033</v>
+        <v>3.732801324338068</v>
       </c>
       <c r="G67">
-        <v>-14.84319789127279</v>
+        <v>-13.84280399803367</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.911944631174745</v>
       </c>
       <c r="E68">
-        <v>-20.10303937220625</v>
+        <v>-12.16543503360749</v>
       </c>
       <c r="F68">
-        <v>1.315272660713836</v>
+        <v>3.252046805529523</v>
       </c>
       <c r="G68">
-        <v>-15.19343209078168</v>
+        <v>-13.10738782503058</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.767468554038232</v>
       </c>
       <c r="E69">
-        <v>-21.1489357290178</v>
+        <v>-12.74172410734961</v>
       </c>
       <c r="F69">
-        <v>1.263387287512209</v>
+        <v>3.259320766799136</v>
       </c>
       <c r="G69">
-        <v>-15.18539077566679</v>
+        <v>-13.5012963965663</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.601121915197607</v>
       </c>
       <c r="E70">
-        <v>-20.599994109808</v>
+        <v>-12.43069945555479</v>
       </c>
       <c r="F70">
-        <v>1.327609729795109</v>
+        <v>2.786187040855686</v>
       </c>
       <c r="G70">
-        <v>-14.62717486319873</v>
+        <v>-14.10907448630279</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.419338479421201</v>
       </c>
       <c r="E71">
-        <v>-19.85631905132036</v>
+        <v>-13.94457737326701</v>
       </c>
       <c r="F71">
-        <v>1.314487142579778</v>
+        <v>3.32342759855021</v>
       </c>
       <c r="G71">
-        <v>-15.39295535988801</v>
+        <v>-12.78778113757826</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.226427230871714</v>
       </c>
       <c r="E72">
-        <v>-20.71908844773572</v>
+        <v>-13.73767592433056</v>
       </c>
       <c r="F72">
-        <v>1.390631722994106</v>
+        <v>3.255483447366026</v>
       </c>
       <c r="G72">
-        <v>-14.80805313982789</v>
+        <v>-12.86959464949027</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.023493895817499</v>
       </c>
       <c r="E73">
-        <v>-20.66319802153305</v>
+        <v>-13.32065780991221</v>
       </c>
       <c r="F73">
-        <v>1.058013888103936</v>
+        <v>3.24955088500679</v>
       </c>
       <c r="G73">
-        <v>-14.18645352246494</v>
+        <v>-13.56875372774726</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.812885712954761</v>
       </c>
       <c r="E74">
-        <v>-20.78045379901366</v>
+        <v>-13.25139479996489</v>
       </c>
       <c r="F74">
-        <v>0.7887727965378223</v>
+        <v>2.84440407030724</v>
       </c>
       <c r="G74">
-        <v>-14.75845785710407</v>
+        <v>-13.68446557070863</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.593758530922182</v>
       </c>
       <c r="E75">
-        <v>-22.18722877797046</v>
+        <v>-13.70900162691399</v>
       </c>
       <c r="F75">
-        <v>0.9894695123778018</v>
+        <v>2.711182728700474</v>
       </c>
       <c r="G75">
-        <v>-14.50125991888532</v>
+        <v>-13.40398291043942</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.36105690260103</v>
       </c>
       <c r="E76">
-        <v>-21.22640433386701</v>
+        <v>-13.41678825614704</v>
       </c>
       <c r="F76">
-        <v>1.269966001884944</v>
+        <v>2.864971659031052</v>
       </c>
       <c r="G76">
-        <v>-14.73200825351806</v>
+        <v>-13.6936092974881</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.110876062370648</v>
       </c>
       <c r="E77">
-        <v>-21.2501878793553</v>
+        <v>-13.96656764304826</v>
       </c>
       <c r="F77">
-        <v>0.6029993415390288</v>
+        <v>2.754576270783514</v>
       </c>
       <c r="G77">
-        <v>-14.2776408440714</v>
+        <v>-12.80182778230139</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.838055055821858</v>
       </c>
       <c r="E78">
-        <v>-22.56617148293232</v>
+        <v>-15.27218556962172</v>
       </c>
       <c r="F78">
-        <v>0.8726331921721719</v>
+        <v>2.221618053884339</v>
       </c>
       <c r="G78">
-        <v>-14.12199554554256</v>
+        <v>-12.9937963864871</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.533380522221173</v>
       </c>
       <c r="E79">
-        <v>-23.4082865093987</v>
+        <v>-15.38392113728698</v>
       </c>
       <c r="F79">
-        <v>0.8912908315619641</v>
+        <v>2.948919158490751</v>
       </c>
       <c r="G79">
-        <v>-13.43886281824118</v>
+        <v>-12.37792235763433</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.189790892671772</v>
       </c>
       <c r="E80">
-        <v>-23.50197157966938</v>
+        <v>-15.75577225195282</v>
       </c>
       <c r="F80">
-        <v>0.6713505051434799</v>
+        <v>2.636650360908062</v>
       </c>
       <c r="G80">
-        <v>-14.09837149257432</v>
+        <v>-11.88728295598664</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.802830166403173</v>
       </c>
       <c r="E81">
-        <v>-23.58725180218183</v>
+        <v>-16.6434029706703</v>
       </c>
       <c r="F81">
-        <v>1.174911972840268</v>
+        <v>2.607760397598616</v>
       </c>
       <c r="G81">
-        <v>-14.21919316257556</v>
+        <v>-12.12178875980646</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.367392205192738</v>
       </c>
       <c r="E82">
-        <v>-23.69920020812545</v>
+        <v>-17.02116374391615</v>
       </c>
       <c r="F82">
-        <v>0.3481873945684835</v>
+        <v>2.62817436684863</v>
       </c>
       <c r="G82">
-        <v>-13.35251385894037</v>
+        <v>-11.88102271437188</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.8831738419688683</v>
       </c>
       <c r="E83">
-        <v>-24.52740829091427</v>
+        <v>-16.4145112519526</v>
       </c>
       <c r="F83">
-        <v>0.6308012988845684</v>
+        <v>2.413078596825475</v>
       </c>
       <c r="G83">
-        <v>-13.58879742571478</v>
+        <v>-11.21745034538928</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.3571455973675884</v>
       </c>
       <c r="E84">
-        <v>-25.84282583524034</v>
+        <v>-18.26754923046929</v>
       </c>
       <c r="F84">
-        <v>0.3006857193407927</v>
+        <v>2.850952694267582</v>
       </c>
       <c r="G84">
-        <v>-12.98135866689606</v>
+        <v>-11.45151584665238</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2014397953047454</v>
       </c>
       <c r="E85">
-        <v>-25.80245901793596</v>
+        <v>-19.32918203445749</v>
       </c>
       <c r="F85">
-        <v>0.5953421234378791</v>
+        <v>2.227216454295417</v>
       </c>
       <c r="G85">
-        <v>-13.66509060294005</v>
+        <v>-12.55163992426204</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.778993296838453</v>
       </c>
       <c r="E86">
-        <v>-27.45150282782912</v>
+        <v>-19.80451783714662</v>
       </c>
       <c r="F86">
-        <v>0.4507798637706509</v>
+        <v>2.208653837260552</v>
       </c>
       <c r="G86">
-        <v>-12.54751498452011</v>
+        <v>-10.59328339996063</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.355441691556161</v>
       </c>
       <c r="E87">
-        <v>-28.98139795810647</v>
+        <v>-20.31863096276342</v>
       </c>
       <c r="F87">
-        <v>0.2643048270513177</v>
+        <v>1.750338847567868</v>
       </c>
       <c r="G87">
-        <v>-13.18608942413567</v>
+        <v>-10.42206198466953</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.909869834648726</v>
       </c>
       <c r="E88">
-        <v>-29.04619589268222</v>
+        <v>-23.00283864606995</v>
       </c>
       <c r="F88">
-        <v>0.1191977725491784</v>
+        <v>1.811135733955673</v>
       </c>
       <c r="G88">
-        <v>-12.1915254015912</v>
+        <v>-9.72352363370115</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.421758714162398</v>
       </c>
       <c r="E89">
-        <v>-30.1130092709352</v>
+        <v>-24.35859583685634</v>
       </c>
       <c r="F89">
-        <v>0.3232503612239739</v>
+        <v>1.915448107782008</v>
       </c>
       <c r="G89">
-        <v>-12.54486985863423</v>
+        <v>-9.244848543632392</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.867529785630798</v>
       </c>
       <c r="E90">
-        <v>-31.11928600865364</v>
+        <v>-24.45473534003918</v>
       </c>
       <c r="F90">
-        <v>0.3275429961077726</v>
+        <v>2.079858953687439</v>
       </c>
       <c r="G90">
-        <v>-11.89807533444467</v>
+        <v>-8.294404161489791</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.227246138531498</v>
       </c>
       <c r="E91">
-        <v>-33.19804577408266</v>
+        <v>-27.1596607919308</v>
       </c>
       <c r="F91">
-        <v>-0.01297515574156704</v>
+        <v>1.630683530832756</v>
       </c>
       <c r="G91">
-        <v>-12.02315105546387</v>
+        <v>-9.29272565322133</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.486981671815728</v>
       </c>
       <c r="E92">
-        <v>-33.20479093611708</v>
+        <v>-27.36370930224242</v>
       </c>
       <c r="F92">
-        <v>0.2685143173745558</v>
+        <v>1.677344258219349</v>
       </c>
       <c r="G92">
-        <v>-11.87568611496257</v>
+        <v>-8.633695352718616</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.636115493894694</v>
       </c>
       <c r="E93">
-        <v>-36.2248642153875</v>
+        <v>-31.4318707197441</v>
       </c>
       <c r="F93">
-        <v>0.008678855240236521</v>
+        <v>1.727365609558503</v>
       </c>
       <c r="G93">
-        <v>-12.24305404290996</v>
+        <v>-8.639690750690235</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.671351608033943</v>
       </c>
       <c r="E94">
-        <v>-37.36980735569481</v>
+        <v>-34.09971702646091</v>
       </c>
       <c r="F94">
-        <v>-0.4452500609196374</v>
+        <v>1.377523389132014</v>
       </c>
       <c r="G94">
-        <v>-11.17886262658354</v>
+        <v>-9.102518259262505</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.599568670545436</v>
       </c>
       <c r="E95">
-        <v>-38.91279430432833</v>
+        <v>-35.62870193346271</v>
       </c>
       <c r="F95">
-        <v>-0.3441731982785455</v>
+        <v>1.715394376543697</v>
       </c>
       <c r="G95">
-        <v>-10.87553720209336</v>
+        <v>-8.926741533309363</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.430115745896297</v>
       </c>
       <c r="E96">
-        <v>-40.5185685450782</v>
+        <v>-37.46148178350609</v>
       </c>
       <c r="F96">
-        <v>-0.06330216232240181</v>
+        <v>1.146077439237862</v>
       </c>
       <c r="G96">
-        <v>-10.74349278271399</v>
+        <v>-8.266029475672697</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.185465026193897</v>
       </c>
       <c r="E97">
-        <v>-42.34139254501572</v>
+        <v>-38.47643734166023</v>
       </c>
       <c r="F97">
-        <v>-0.6644848463527933</v>
+        <v>1.157969486956897</v>
       </c>
       <c r="G97">
-        <v>-11.60485700548588</v>
+        <v>-8.578495316396808</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.881220300184238</v>
       </c>
       <c r="E98">
-        <v>-45.60714686038727</v>
+        <v>-42.02900255830758</v>
       </c>
       <c r="F98">
-        <v>-0.6248328094949781</v>
+        <v>0.9012650114174017</v>
       </c>
       <c r="G98">
-        <v>-11.62834201554147</v>
+        <v>-8.335365541447192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.555202174978606</v>
       </c>
       <c r="E99">
-        <v>-46.78944311854685</v>
+        <v>-43.35870290965384</v>
       </c>
       <c r="F99">
-        <v>-0.8857238116219377</v>
+        <v>0.223018405688769</v>
       </c>
       <c r="G99">
-        <v>-11.72457626382254</v>
+        <v>-7.869836627714879</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.213395551759127</v>
       </c>
       <c r="E100">
-        <v>-48.59071384644485</v>
+        <v>-45.70392714264219</v>
       </c>
       <c r="F100">
-        <v>-1.043054700232396</v>
+        <v>0.9100165703061202</v>
       </c>
       <c r="G100">
-        <v>-11.59933501552637</v>
+        <v>-9.700896054940232</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.909137172918096</v>
       </c>
       <c r="E101">
-        <v>-50.43193816839403</v>
+        <v>-47.03437242796271</v>
       </c>
       <c r="F101">
-        <v>-1.159594867431839</v>
+        <v>0.1737089301586041</v>
       </c>
       <c r="G101">
-        <v>-11.7513883721451</v>
+        <v>-8.840849429292971</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.606506555935041</v>
       </c>
       <c r="E102">
-        <v>-52.96317399972146</v>
+        <v>-50.10778207409547</v>
       </c>
       <c r="F102">
-        <v>-1.295754775364703</v>
+        <v>-0.1319597730214905</v>
       </c>
       <c r="G102">
-        <v>-12.44120012507196</v>
+        <v>-9.130790318167881</v>
       </c>
     </row>
   </sheetData>
